--- a/04_Figures/F6/c_data/Figure_6_data.xlsx
+++ b/04_Figures/F6/c_data/Figure_6_data.xlsx
@@ -2548,7 +2548,7 @@
     <t xml:space="preserve">generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-27 02:54</t>
+    <t xml:space="preserve">2026-02-28 16:07</t>
   </si>
   <si>
     <t xml:space="preserve">n_subjects</t>
